--- a/task.xlsx
+++ b/task.xlsx
@@ -1,25 +1,183 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data Analytics\Excel\Prac\Logical_method\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22009C87-917B-4368-BA29-C8AF09466FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
+  <si>
+    <t>seat_no</t>
+  </si>
+  <si>
+    <t>customer_name</t>
+  </si>
+  <si>
+    <t>baggage_weight</t>
+  </si>
+  <si>
+    <t>seat_class</t>
+  </si>
+  <si>
+    <t>ticket_no</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> to</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>company</t>
+  </si>
+  <si>
+    <t>cust1</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>T-101</t>
+  </si>
+  <si>
+    <t>NAGPUR</t>
+  </si>
+  <si>
+    <t>DELHI</t>
+  </si>
+  <si>
+    <t>indigo</t>
+  </si>
+  <si>
+    <t>cust2</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>T-102</t>
+  </si>
+  <si>
+    <t>PUNE</t>
+  </si>
+  <si>
+    <t>MUMBAI</t>
+  </si>
+  <si>
+    <t>AIR INDIA</t>
+  </si>
+  <si>
+    <t>ARC_cust</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>T-103</t>
+  </si>
+  <si>
+    <t>DUBAI</t>
+  </si>
+  <si>
+    <t>qatar airlines</t>
+  </si>
+  <si>
+    <t>Vigo_cust</t>
+  </si>
+  <si>
+    <t>T-104</t>
+  </si>
+  <si>
+    <t>arc2</t>
+  </si>
+  <si>
+    <t>T-105</t>
+  </si>
+  <si>
+    <t>hyderabad</t>
+  </si>
+  <si>
+    <t>DB_user1</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>T-106</t>
+  </si>
+  <si>
+    <t>if else</t>
+  </si>
+  <si>
+    <t>if else if</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>20+budget</t>
+  </si>
+  <si>
+    <t>Travel time of my flight is 30 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My scheduled meeting is at </t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>Problem + Logic = Output</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -29,15 +187,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +215,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="21" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +521,416 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C1:Q15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" customWidth="1"/>
+    <col min="14" max="14" width="16.5546875" customWidth="1"/>
+    <col min="15" max="15" width="17.21875" customWidth="1"/>
+    <col min="16" max="16" width="21.33203125" customWidth="1"/>
+    <col min="17" max="17" width="19.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1">
+        <v>60</v>
+      </c>
+      <c r="K1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="3">
+        <v>0.89583333333333337</v>
+      </c>
+    </row>
+    <row r="2" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2">
+        <v>80</v>
+      </c>
+      <c r="K2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="3">
+        <v>2.0833333333333332E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C7" s="2">
+        <v>101</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="2">
+        <v>60</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="6">
+        <f>N$1-K7</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="N7" s="6" t="str">
+        <f>IF(M7&gt;N$2,"I can travel","I can't travel")</f>
+        <v>I can travel</v>
+      </c>
+      <c r="O7" s="6" t="str">
+        <f>IF(H$1&gt;=H7,"Budget is good ","Budget is low")</f>
+        <v xml:space="preserve">Budget is good </v>
+      </c>
+      <c r="P7" s="6" t="str">
+        <f>IF(H$1&gt;H7,"Budget is good",IF(H$2&gt;H7,"Increased budget is good","Budget is low"))</f>
+        <v>Increased budget is good</v>
+      </c>
+      <c r="Q7" s="6" t="str">
+        <f>IF(M7&lt;0, "Too late", IF(M7 = $M$8, "Best choice", "Wait"))</f>
+        <v>Wait</v>
+      </c>
+    </row>
+    <row r="8" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C8" s="2">
+        <v>102</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2">
+        <v>30</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="2">
+        <v>50</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="6">
+        <f t="shared" ref="M8:M12" si="0">N$1-K8</f>
+        <v>0.25</v>
+      </c>
+      <c r="N8" s="6" t="str">
+        <f t="shared" ref="N8:N12" si="1">IF(M8&gt;N$2,"I can travel","I can't travel")</f>
+        <v>I can travel</v>
+      </c>
+      <c r="O8" s="6" t="str">
+        <f t="shared" ref="O8:O12" si="2">IF(H$1&gt;=H8,"Budget is good ","Budget is low")</f>
+        <v xml:space="preserve">Budget is good </v>
+      </c>
+      <c r="P8" s="6" t="str">
+        <f t="shared" ref="P8:P12" si="3">IF(H$1&gt;H8,"Budget is good",IF(H$2&gt;H8,"Increased budget is good","Budget is low"))</f>
+        <v>Budget is good</v>
+      </c>
+      <c r="Q8" s="6" t="str">
+        <f t="shared" ref="Q8:Q12" si="4">IF(M8&lt;0, "Too late", IF(M8 = $M$8, "Best choice", "Wait"))</f>
+        <v>Best choice</v>
+      </c>
+    </row>
+    <row r="9" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C9" s="2">
+        <v>103</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2">
+        <v>50</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="2">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="6">
+        <f t="shared" si="0"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="N9" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>I can travel</v>
+      </c>
+      <c r="O9" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Budget is low</v>
+      </c>
+      <c r="P9" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>Budget is low</v>
+      </c>
+      <c r="Q9" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>Wait</v>
+      </c>
+    </row>
+    <row r="10" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C10" s="2">
+        <v>104</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="2">
+        <v>40</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="2">
+        <v>120</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="5">
+        <v>2.361111111111111E-2</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="6">
+        <f t="shared" si="0"/>
+        <v>0.87222222222222223</v>
+      </c>
+      <c r="N10" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>I can travel</v>
+      </c>
+      <c r="O10" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>Budget is low</v>
+      </c>
+      <c r="P10" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>Budget is low</v>
+      </c>
+      <c r="Q10" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>Wait</v>
+      </c>
+    </row>
+    <row r="11" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C11" s="2">
+        <v>105</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="2">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="2">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0.99652777777777779</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" s="6">
+        <f t="shared" si="0"/>
+        <v>-0.10069444444444442</v>
+      </c>
+      <c r="N11" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>I can't travel</v>
+      </c>
+      <c r="O11" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Budget is good </v>
+      </c>
+      <c r="P11" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>Budget is good</v>
+      </c>
+      <c r="Q11" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>Too late</v>
+      </c>
+    </row>
+    <row r="12" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C12" s="2">
+        <v>106</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="2">
+        <v>30</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="2">
+        <v>60</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="6">
+        <f t="shared" si="0"/>
+        <v>0.39236111111111116</v>
+      </c>
+      <c r="N12" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>I can travel</v>
+      </c>
+      <c r="O12" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">Budget is good </v>
+      </c>
+      <c r="P12" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v>Increased budget is good</v>
+      </c>
+      <c r="Q12" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>Wait</v>
+      </c>
+    </row>
+    <row r="15" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="G15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>